--- a/FACTURAS-RECIBIDAS-NUEVO.xlsx
+++ b/FACTURAS-RECIBIDAS-NUEVO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.109375" bestFit="1" customWidth="1" min="4" max="4"/>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>00104709</t>
+          <t>00104710</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>00-114919</t>
+          <t>00-114920</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1898,100 +1898,26 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>513361.95</v>
+        <v>865064.83</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>513361.95</v>
+        <v>865064.83</v>
       </c>
       <c r="O20" t="n">
-        <v>82137.91</v>
+        <v>138410.37</v>
       </c>
       <c r="P20" t="n">
-        <v>595499.86</v>
+        <v>1003475.2</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-22T15:37:41</t>
+          <t>2026-05-22T15:37:59</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
-        <is>
-          <t>* Emisor (Proveedor): SOLARI, C.A. (RIF: J-30880787-7)
- * Dirección Fiscal del Emisor: CALLE ANDRÉS ELOY BLANCO - LOCAL Nro. 15-10B BARRIO SUCRE - BARCELONA - EDO. ANZOATEGUI Z.P. 6001
- * Teléfono del Proveedor: (0281) 274.31.98 / (0414) 815.95.46 / (0414) 819.59.35
- * Número de Documento: 00104709
- * Número de Control: 00-114919
- * Fecha de Emisión: 20/05/2026
-### Desglose Financiero (Bolívares)
- * Sub-Total: Bs. 51</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Factura recibida / compra</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>00104710</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>00-114920</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SOLARI, C.A</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>J-30880787-7</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(0281) 274.31.98 / (0414) 815.95.46 / (0414) 819.59.35</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>CALLE ANDRÉS ELOY BLANCO - LOCAL Nro. 15-10B BARRIO SUCRE - BARCELONA - EDO. ANZOATEGUI Z.P. 6001</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>865064.83</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>865064.83</v>
-      </c>
-      <c r="O21" t="n">
-        <v>138410.37</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1003475.2</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>2026-05-22T15:37:59</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
         <is>
           <t>* Emisor (Proveedor): SOLARI, C.A. (RIF: J-30880787-7)
  * Dirección Fiscal del Emisor: CALLE ANDRÉS ELOY BLANCO - LOCAL Nro. 15-10B BARRIO SUCRE - BARCELONA - EDO. ANZOATEGUI Z.P. 6001
@@ -2004,68 +1930,68 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Factura recibida / compra</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>014167</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>00-0015234</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>REPRESENTACIONES SU MAYOR 33, C.A</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>J-40451540-2</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>(0281) 282.70.84</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Calle El Milagro Local N° 14 - Sector Centro - Puerto La Cruz Edo. Anzoátegui.</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="L21" t="n">
         <v>57218.08</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N21" t="n">
         <v>57218.08</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O21" t="n">
         <v>9154.889999999999</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P21" t="n">
         <v>66372.97</v>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>2026-05-23T15:35:25</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>### Factura 1
  * Emisor (Proveedor): REPRESENTACIONES SU MAYOR 33, C.A. (RIF: J-40451540-2) 
@@ -2080,68 +2006,68 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Factura recibida / compra</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>014168</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>00-0015235</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>REPRESENTACIONES SU MAYOR 33, C.A</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>J-40451540-2</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>(0281) 282.70.84</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Calle El Milagro Local Nº 14 - Sector Centro - Puerto La Cruz Edo. Anzoátegui.</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="L22" t="n">
         <v>30558.46</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N22" t="n">
         <v>30558.46</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O22" t="n">
         <v>4883.35</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P22" t="n">
         <v>35441.81</v>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>2026-05-23T15:35:39</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>### Factura 2
  * Emisor (Proveedor): REPRESENTACIONES SU MAYOR 33, C.A. (RIF: J-40451540-2) 
@@ -2156,68 +2082,68 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Factura recibida / compra</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>014169</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>00-0015236</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>REPRESENTACIONES SU MAYOR 33, C.A</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>J-40451540-2</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>(0281) 282.70.84</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Calle El Milagro Local N° 14 - Sector Centro - Puerto La Cruz Edo. Anzoátegui.</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="L23" t="n">
         <v>91675.38</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N23" t="n">
         <v>91675.38</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O23" t="n">
         <v>14668.06</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P23" t="n">
         <v>106343.44</v>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>2026-05-23T15:35:53</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>### Factura 3
  * Emisor (Proveedor): REPRESENTACIONES SU MAYOR 33, C.A. (RIF: J-40451540-2) 
@@ -2232,68 +2158,68 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Factura recibida / compra</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>014170</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>00-0015237</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>REPRESENTACIONES SU MAYOR 33, C.A</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>J-40451540-2</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>(0281) 282.70.84</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Calle El Milagro Local N° 14 - Sector Centro - Puerto La Cruz Edo. Anzoátegui.</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="L24" t="n">
         <v>98088.77</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N24" t="n">
         <v>98088.77</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O24" t="n">
         <v>15695.8</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P24" t="n">
         <v>113784.57</v>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>2026-05-23T15:36:07</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>### Factura 4
  * Emisor (Proveedor): REPRESENTACIONES SU MAYOR 33, C.A. (RIF: J-40451540-2) 
@@ -2308,68 +2234,68 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Factura recibida / compra</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>014171</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>00-0015238</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>REPRESENTACIONES SU MAYOR 33, C.A</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>J-40451540-2</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>(0281) 282.70.84</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Calle El Milagro Local Nº 14 - Sector Centro - Puerto La Cruz Edo. Anzoátegui.</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="L25" t="n">
         <v>35212.24</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N25" t="n">
         <v>35212.24</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O25" t="n">
         <v>5640.36</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P25" t="n">
         <v>40852.6</v>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>2026-05-23T15:36:20</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t xml:space="preserve">### Factura 5 (Pág. 5)
  * Emisor (Proveedor): REPRESENTACIONES SU MAYOR 33, C.A. (RIF: J-40451540-2) 
@@ -2384,68 +2310,68 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Factura recibida / compra</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>014172</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>00-0015239</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>REPRESENTACIONES SU MAYOR 33, C.A</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>J-40451540-2</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>(0281) 282.70.84</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Calle El Milagro Local Nº 14 - Sector Centro - Puerto La Cruz Edo. Anzoátegui.</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="L26" t="n">
         <v>78076.87</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N26" t="n">
         <v>78076.87</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O26" t="n">
         <v>12492.3</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P26" t="n">
         <v>90569.17</v>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>2026-05-23T15:36:40</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>### Factura 6
  * Emisor (Proveedor): REPRESENTACIONES SU MAYOR 33, C.A. (RIF: J-40451540-2) 
@@ -2460,68 +2386,68 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Factura recibida / compra</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>014173</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>00-0015240</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>REPRESENTACIONES SU MAYOR 33, C.A</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>J-40451540-2</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>(0281) 282.70.84</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Calle El Milagro Local Nº 14 - Sector Centro - Puerto La Cruz Edo. Anzoátegui.</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="L27" t="n">
         <v>79693.41</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N27" t="n">
         <v>79693.41</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O27" t="n">
         <v>12750.95</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P27" t="n">
         <v>92444.36</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>2026-05-23T15:36:51</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>### Factura 7
  * Emisor (Proveedor): REPRESENTACIONES SU MAYOR 33, C.A. (RIF: J-40451540-2) 
@@ -2536,68 +2462,68 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Factura recibida / compra</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>014174</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>00-0015241</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>REPRESENTACIONES SU MAYOR 33, C.A</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>J-40451540-2</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>(0281) 282.70.84</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Calle El Milagro Local Nº 14 - Sector Centro - Puerto La Cruz Edo. Anzoátegui.</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="L28" t="n">
         <v>124668.4</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N28" t="n">
         <v>124668.4</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O28" t="n">
         <v>19946.94</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P28" t="n">
         <v>144615.34</v>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>2026-05-23T15:37:04</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>### Factura 8
  * Emisor (Proveedor): REPRESENTACIONES SU MAYOR 33, C.A. (RIF: J-40451540-2) 
@@ -2612,68 +2538,68 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Factura recibida / compra</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>014175</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>00-0015242</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>REPRESENTACIONES SU MAYOR 33, C.A</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>J-40451540-2</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>(0281) 282.70.84</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Calle El Milagro Local Nº 14 - Sector Centro - Puerto La Cruz Edo. Anzoátegui.</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="L29" t="n">
         <v>128550.38</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N29" t="n">
         <v>128550.38</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O29" t="n">
         <v>20568.06</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P29" t="n">
         <v>149118.44</v>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>2026-05-23T15:37:16</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>### Factura 9
  * Emisor (Proveedor): REPRESENTACIONES SU MAYOR 33, C.A. (RIF: J-40451540-2) 
@@ -2688,6 +2614,78 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>B00093025</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>00-116630</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPERMEABILIZADORA MARKINA - XEMEIN, C.A</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>J-095161609</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(0286) 994.47.66 / 994.42.66 / 994.15.92</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Av. Manzana 35 Local Galpón Nro 7, Zona Industrial Los Pinos. Puerto Ordaz, Ciudad Guayana - Edo. Bolívar. Zona Postal 8050.</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>32379.8</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>32379.8</v>
+      </c>
+      <c r="O30" t="n">
+        <v>5180.77</v>
+      </c>
+      <c r="P30" t="n">
+        <v>37560.57</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:48:42</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>* Emisor (Proveedor): DISTRIBUIDORA E IMPERMEABILIZADORA MARKINA - XEMEIN, C.A. (RIF: J095161609)
+ * Dirección Fiscal del Emisor: Av. Manzana 35 Local Galpón Nro 7, Zona Industrial Los Pinos. Puerto Ordaz, Ciudad Guayana - Edo. Bolívar. Zona Postal 8050.
+ * Teléfono del Proveedor: (0286) 994.47.66 / 994.42.66 / 994.15.92
+ * Número de Documento: B00093025
+ * Número de Control: 00-116630
+ * Fecha de Emisión: 21/04/2026</t>
+        </is>
+      </c>
+    </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
@@ -2696,223 +2694,669 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>28/03/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>06992911</t>
+          <t>B00093101</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>00-00963280</t>
+          <t>00-116765</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>DISTRIBUIDORA E IMPERMEABILIZADORA MARKINA - XEMEIN, C.A</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>J-095161609</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(0286) 994.47.66 / 994.42.66 / 994.15.92</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Av. Manzana 35 Local Galpón Nro 7, Zona Industrial Los Pinos. Puerto Ordaz, Ciudad Guayana - Edo. Bolívar. Zona Postal 8050.</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>70409.75999999999</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>70409.75999999999</v>
+      </c>
+      <c r="O31" t="n">
+        <v>11265.56</v>
+      </c>
+      <c r="P31" t="n">
+        <v>81675.32000000001</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:15:42</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>* Emisor (Proveedor): DISTRIBUIDORA E IMPERMEABILIZADORA MARKINA - XEMEIN, C.A. (RIF: J095161609)
+ * Dirección Fiscal del Emisor: Av. Manzana 35 Local Galpón Nro 7, Zona Industrial Los Pinos. Puerto Ordaz, Ciudad Guayana - Edo. Bolívar. Zona Postal 8050.
+ * Teléfono del Proveedor: (0286) 994.47.66 / 994.42.66 / 994.15.92
+ * Número de Documento: B00093101
+ * Número de Control: 00-116765
+ * Fecha de Emisión: 06/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>00104709</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>00-114919</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>SOLARI, C.A</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>J-30880787-7</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(0281) 274.31.98 - (0414) 815.95.46 / (0414) 819.59.35</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Calle Andrés Eloy Blanco - Local Nro. 15-10B Barrio Sucre - Barcelona - Edo. Anzoátegui Z.P. 6001</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>513361.95</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>513361.95</v>
+      </c>
+      <c r="O32" t="n">
+        <v>82137.91</v>
+      </c>
+      <c r="P32" t="n">
+        <v>595499.86</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:19:57</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>* Emisor (Proveedor): SOLARI, C.A. (RIF: J-30880787-7)
+ * Dirección Fiscal del Emisor: Calle Andrés Eloy Blanco - Local Nro. 15-10B Barrio Sucre - Barcelona - Edo. Anzoátegui Z.P. 6001
+ * Teléfono del Proveedor: (0281) 274.31.98 - (0414) 815.95.46 / (0414) 819.59.35
+ * Número de Documento: 00104709
+ * Número de Control: 00-114919
+ * Fecha de Emisión: 20/05/2026
+### Desglose Financiero (Bolívares)
+ * Sub-Total: Bs. 51</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0080542</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>00-01018730</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>FEBECA, C.A</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>J-000033927</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0 800 SILLA 00 - 0 800 74552 00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>AV FUNDO LA UNION LOCAL PARCELA NRO L13 Y L19 ZONA INDUSTRIAL CASTILLITO VALENCIA CARABOBO ZONA POSTAL 2010</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>59181.48</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1161.79</v>
+      </c>
+      <c r="N33" t="n">
+        <v>58019.69</v>
+      </c>
+      <c r="O33" t="n">
+        <v>9283.15</v>
+      </c>
+      <c r="P33" t="n">
+        <v>68464.63</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:20:34</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>* Emisor (Proveedor): FEBECA, C.A. (RIF: J-000033927)
+ * Dirección Fiscal del Emisor: AV FUNDO LA UNION LOCAL PARCELA NRO L13 Y L19 ZONA INDUSTRIAL CASTILLITO VALENCIA CARABOBO ZONA POSTAL 2010
+ * Teléfono del Proveedor: 0 800 SILLA 00 - 0 800 74552 00
+ * Número de Documento: 0080542
+ * Número de Control: 00-01018730
+ * Fecha de Emisión: 26-05-2026
+#### Desglose Financiero (Bolívares)
+ * Sub-Total: Bs. 59.181,48
+ * B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0080543</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>00-01018731</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>FEBECA, C.A</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>J-000033927</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0 800 SILLA 00 - 0 800 74552 00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>AV FUNDO LA UNION LOCAL PARCELA NRO L13 Y L19 ZONA INDUSTRIAL CASTILLITO VALENCIA CARABOBO ZONA POSTAL 2010</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>55326.72</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1086.83</v>
+      </c>
+      <c r="N34" t="n">
+        <v>54239.89</v>
+      </c>
+      <c r="O34" t="n">
+        <v>8678.379999999999</v>
+      </c>
+      <c r="P34" t="n">
+        <v>64005.1</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:20:47</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>* Emisor (Proveedor): FEBECA, C.A. (RIF: J-000033927)
+ * Dirección Fiscal del Emisor: AV FUNDO LA UNION LOCAL PARCELA NRO L13 Y L19 ZONA INDUSTRIAL CASTILLITO VALENCIA CARABOBO ZONA POSTAL 2010
+ * Teléfono del Proveedor: 0 800 SILLA 00 - 0 800 74552 00
+ * Número de Documento: 0080543
+ * Número de Control: 00-01018731
+ * Fecha de Emisión: 26-05-2026
+#### Desglose Financiero (Bolívares)
+ * Sub-Total: Bs. 55.326,72
+ * B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0080544</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>00-01018732</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>FEBECA, C.A</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>J-000033927</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0 800 SILLA 00 - 0 800 74552 00</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>AV FUNDO LA UNION LOCAL PARCELA NRO L13 Y L19 ZONA INDUSTRIAL CASTILLITO VALENCIA CARABOBO ZONA POSTAL 2010</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>93901.24000000001</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1841.73</v>
+      </c>
+      <c r="N35" t="n">
+        <v>92059.50999999999</v>
+      </c>
+      <c r="O35" t="n">
+        <v>14729.52</v>
+      </c>
+      <c r="P35" t="n">
+        <v>108630.76</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:22:25</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>* Emisor (Proveedor): FEBECA, C.A. (RIF: J-000033927)
+ * Dirección Fiscal del Emisor: AV FUNDO LA UNION LOCAL PARCELA NRO L13 Y L19 ZONA INDUSTRIAL CASTILLITO VALENCIA CARABOBO ZONA POSTAL 2010
+ * Teléfono del Proveedor: 0 800 SILLA 00 - 0 800 74552 00
+ * Número de Documento: 0080544
+ * Número de Control: 00-01018732
+ * Fecha de Emisión: 26-05-2026
+#### Desglose Financiero (Bolívares)
+ * Sub-Total: Bs. 93.901,24
+ * B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>07021585</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>00-01067978</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>FEBECA, C.A</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>J-000033927</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>0 800 FEBECA 1 - 0 800 332322 1</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>AV FUNDO LA UNION LOCAL PARCELA NRO L13 Y L19 ZONA INDUSTRIAL CASTILLITO VALENCIA CARABOBO ZONA POSTAL 2010</t>
         </is>
       </c>
-      <c r="L31" t="n">
-        <v>345680.93</v>
-      </c>
-      <c r="M31" t="n">
-        <v>8018.91</v>
-      </c>
-      <c r="N31" t="n">
-        <v>337662.02</v>
-      </c>
-      <c r="O31" t="n">
-        <v>54025.92</v>
-      </c>
-      <c r="P31" t="n">
-        <v>399706.85</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>2026-05-27T15:25:14</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
+      <c r="L36" t="n">
+        <v>34439.2</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2989.74</v>
+      </c>
+      <c r="N36" t="n">
+        <v>31444.46</v>
+      </c>
+      <c r="O36" t="n">
+        <v>5031.91</v>
+      </c>
+      <c r="P36" t="n">
+        <v>39471.11</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:22:36</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t xml:space="preserve">* Emisor (Proveedor): FEBECA, C.A. (RIF: J-000033927)
  * Dirección Fiscal del Emisor: AV FUNDO LA UNION LOCAL PARCELA NRO L13 Y L19 ZONA INDUSTRIAL CASTILLITO VALENCIA CARABOBO ZONA POSTAL 2010
  * Teléfono del Proveedor: 0 800 FEBECA 1 - 0 800 332322 1
- * Número de Documento: 06992911
- * Número de Control: 00-00963280
- * Fecha de Emisión: 28/03/2026
-### Desglose Financiero (Bolívares)
- * Sub-Total: Bs. 345.680,93
+ * Número de Documento: 07021585
+ * Número de Control: 00-01067978
+ * Fecha de Emisión: 28-05-2026
+#### Desglose Financiero (Bolívares)
+ * Sub-Total: Bs. 34.439,20
  * </t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Factura recibida / compra</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>28/03/2026</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>06992911</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>00-00963280</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>07021677</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>00-01068361</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>FEBECA, C.A</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>J-000033927</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>0 800 FEBECA 1 - 0 800 332322 1</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>AV FUNDO LA UNION LOCAL PARCELA NRO L13 Y L19 ZONA INDUSTRIAL CASTILLITO VALENCIA CARABOBO ZONA POSTAL 2010</t>
         </is>
       </c>
-      <c r="L32" t="n">
-        <v>345680.93</v>
-      </c>
-      <c r="M32" t="n">
-        <v>8018.91</v>
-      </c>
-      <c r="N32" t="n">
-        <v>337662.02</v>
-      </c>
-      <c r="O32" t="n">
-        <v>54025.92</v>
-      </c>
-      <c r="P32" t="n">
-        <v>399706.85</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>2026-05-28T10:29:10</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">* Emisor (Proveedor): FEBECA, C.A. (RIF: J-000033927)
+      <c r="L37" t="n">
+        <v>358420.38</v>
+      </c>
+      <c r="M37" t="n">
+        <v>8315.73</v>
+      </c>
+      <c r="N37" t="n">
+        <v>350104.65</v>
+      </c>
+      <c r="O37" t="n">
+        <v>56016.74</v>
+      </c>
+      <c r="P37" t="n">
+        <v>414437.12</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:22:46</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>* Emisor (Proveedor): FEBECA, C.A. (RIF: J-000033927)
  * Dirección Fiscal del Emisor: AV FUNDO LA UNION LOCAL PARCELA NRO L13 Y L19 ZONA INDUSTRIAL CASTILLITO VALENCIA CARABOBO ZONA POSTAL 2010
  * Teléfono del Proveedor: 0 800 FEBECA 1 - 0 800 332322 1
- * Número de Documento: 06992911
- * Número de Control: 00-00963280
- * Fecha de Emisión: 28/03/2026
-### Desglose Financiero (Bolívares)
- * Sub-Total: Bs. 345.680,93
- * </t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Factura recibida / compra</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>28/03/2026</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>06992911</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>00-00963280</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
+ * Número de Documento: 07021677
+ * Número de Control: 00-01068361
+ * Fecha de Emisión: 28-05-2026
+#### Desglose Financiero (Bolívares)
+ * Sub-Total: Bs. 358.420,38
+ *</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>07021678</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>00-01068363</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>FEBECA, C.A</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>J-000033927</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>0 800 FEBECA 1 - 0 800 332322 1</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>AV FUNDO LA UNION LOCAL PARCELA NRO L13 Y L19 ZONA INDUSTRIAL CASTILLITO VALENCIA CARABOBO ZONA POSTAL 2010</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
-        <v>345680.93</v>
-      </c>
-      <c r="M33" t="n">
-        <v>8018.91</v>
-      </c>
-      <c r="N33" t="n">
-        <v>337662.02</v>
-      </c>
-      <c r="O33" t="n">
-        <v>54025.92</v>
-      </c>
-      <c r="P33" t="n">
-        <v>399706.85</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>2026-05-28T10:38:25</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">* Emisor (Proveedor): FEBECA, C.A. (RIF: J-000033927)
+      <c r="L38" t="n">
+        <v>112183.36</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2603.09</v>
+      </c>
+      <c r="N38" t="n">
+        <v>109580.27</v>
+      </c>
+      <c r="O38" t="n">
+        <v>17532.84</v>
+      </c>
+      <c r="P38" t="n">
+        <v>129716.2</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:23:02</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>* Emisor (Proveedor): FEBECA, C.A. (RIF: J-000033927)
  * Dirección Fiscal del Emisor: AV FUNDO LA UNION LOCAL PARCELA NRO L13 Y L19 ZONA INDUSTRIAL CASTILLITO VALENCIA CARABOBO ZONA POSTAL 2010
  * Teléfono del Proveedor: 0 800 FEBECA 1 - 0 800 332322 1
- * Número de Documento: 06992911
- * Número de Control: 00-00963280
- * Fecha de Emisión: 28/03/2026
-### Desglose Financiero (Bolívares)
- * Sub-Total: Bs. 345.680,93
- * </t>
+ * Número de Documento: 07021678
+ * Número de Control: 00-01068363
+ * Fecha de Emisión: 28-05-2026
+#### Desglose Financiero (Bolívares)
+ * Sub-Total: Bs. 112.183,36
+ *</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Factura recibida / compra</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>07022499</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>00-01070592</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>FEBECA, C.A</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>J-000033927</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0 800 FEBECA 1 - 0 800 332322 1</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>AV FUNDO LA UNION LOCAL PARCELA NRO L13 Y L19 ZONA INDUSTRIAL CASTILLITO VALENCIA CARABOBO ZONA POSTAL 2010</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>231961.17</v>
+      </c>
+      <c r="M39" t="n">
+        <v>10520.47</v>
+      </c>
+      <c r="N39" t="n">
+        <v>221440.7</v>
+      </c>
+      <c r="O39" t="n">
+        <v>35430.51</v>
+      </c>
+      <c r="P39" t="n">
+        <v>267391.68</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:23:20</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>* Emisor (Proveedor): FEBECA, C.A. (RIF: J-000033927)
+ * Dirección Fiscal del Emisor: AV FUNDO LA UNION LOCAL PARCELA NRO L13 Y L19 ZONA INDUSTRIAL CASTILLITO VALENCIA CARABOBO ZONA POSTAL 2010
+ * Teléfono del Proveedor: 0 800 FEBECA 1 - 0 800 332322 1
+ * Número de Documento: 07022499
+ * Número de Control: 00-01070592
+ * Fecha de Emisión: 29-05-2026
+#### Desglose Financiero (Bolívares)
+ * Sub-Total: Bs. 231.961,17
+ *</t>
         </is>
       </c>
     </row>
